--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2770,6 +2770,498 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115105789</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granfallsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654691</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6675460</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115105760</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Granfallsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>654721</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6675453</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115105776</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90281</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Granfallsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>654684</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6675667</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115105757</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granfallsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>654703</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6675483</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,11 +3391,11 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57510</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">

--- a/artfynd/A 56952-2023 artfynd.xlsx
+++ b/artfynd/A 56952-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>121381724</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
